--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:42:41+00:00</t>
+    <t>2026-06-15T15:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T15:11:11+00:00</t>
+    <t>2026-06-15T15:19:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T15:19:45+00:00</t>
+    <t>2026-06-16T07:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:24:54+00:00</t>
+    <t>2026-06-16T07:41:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:41:08+00:00</t>
+    <t>2026-06-16T07:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:48:16+00:00</t>
+    <t>2026-06-16T08:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:08:12+00:00</t>
+    <t>2026-06-16T08:19:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
+++ b/preview/pr-2/ValueSet-dem-urbanizitaet-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:19:50+00:00</t>
+    <t>2026-06-16T08:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
